--- a/data/trans_camb/P1409-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1409-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,11</t>
+          <t>-1,04; 2,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,97</t>
+          <t>0,3; 4,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,08</t>
+          <t>-0,39; 3,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,83</t>
+          <t>1,24; 4,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,28</t>
+          <t>-0,22; 2,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,23</t>
+          <t>1,52; 3,95</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104,1%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 115,96</t>
+          <t>-32,1; 111,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 252,68</t>
+          <t>4,08; 223,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 118,03</t>
+          <t>-12,07; 116,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,88; 199,09</t>
+          <t>30,06; 182,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 94,9</t>
+          <t>-6,45; 87,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,3; 176,03</t>
+          <t>41,37; 163,28</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>1,97</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,84</t>
+          <t>0,06; 1,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,11</t>
+          <t>0,82; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,66</t>
+          <t>0,3; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 14,13</t>
+          <t>0,89; 3,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,95</t>
+          <t>0,5; 1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,97</t>
+          <t>1,2; 2,83</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>102,69%</t>
+          <t>113,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197,45%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>159,87%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 146,03</t>
+          <t>3,08; 148,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 228,42</t>
+          <t>40,15; 251,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 150,76</t>
+          <t>9,89; 145,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,33; 719,02</t>
+          <t>29,33; 170,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 115,08</t>
+          <t>20,59; 114,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,93; 466,1</t>
+          <t>51,8; 173,84</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>2,1</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,83</t>
+          <t>-1,71; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,1</t>
+          <t>0,27; 4,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,01</t>
+          <t>-1,14; 3,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,97</t>
+          <t>-0,34; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,82</t>
+          <t>-0,84; 1,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,92</t>
+          <t>0,64; 3,65</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>117,59%</t>
+          <t>145,97%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,23; 248,88</t>
+          <t>-67,49; 266,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 501,45</t>
+          <t>-0,77; 636,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 178,77</t>
+          <t>-33,94; 196,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 191,15</t>
+          <t>-10,11; 205,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 109,74</t>
+          <t>-30,79; 131,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 191,57</t>
+          <t>20,42; 257,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,0</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,81</t>
+          <t>1,14; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,23</t>
+          <t>0,37; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,0</t>
+          <t>1,29; 2,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,59</t>
+          <t>0,38; 1,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,83</t>
+          <t>1,38; 2,6</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>101,12%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132,08%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>116,42%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 81,7</t>
+          <t>-4,28; 83,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,74; 164,1</t>
+          <t>48,76; 179,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,3; 95,78</t>
+          <t>10,95; 89,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49,24; 381,2</t>
+          <t>39,54; 128,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,4; 78,31</t>
+          <t>13,7; 72,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,51; 303,18</t>
+          <t>51,12; 124,52</t>
         </is>
       </c>
     </row>
